--- a/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:52:14+00:00</t>
+    <t>2026-09-01T10:04:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:04:58+00:00</t>
+    <t>2026-09-01T10:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:41:01+00:00</t>
+    <t>2026-09-01T10:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:46:34+00:00</t>
+    <t>2026-09-01T11:05:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:05:48+00:00</t>
+    <t>2026-09-01T11:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/update-ig-template/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:14:45+00:00</t>
+    <t>2026-09-01T11:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
